--- a/LISTAS_ORDENADAS/MI/Rodillos/MINI RODILLOS DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Rodillos/MINI RODILLOS DISMAY.xlsx
@@ -712,13 +712,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45168.54418903344</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -755,27 +751,6 @@
       </c>
       <c r="B10" s="6" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="G32" s="18" t="n"/>
     </row>
@@ -815,7 +790,7 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>105.3</v>
+        <v>110</v>
       </c>
       <c r="E34" s="7" t="n"/>
     </row>
@@ -924,7 +899,6 @@
       </c>
       <c r="E39" s="7" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1" s="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
@@ -939,9 +913,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
